--- a/moment_list.xlsx
+++ b/moment_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\NetworkNNE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F6DA65-6D2C-4DB6-95D6-B7D8D4EE3161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6D84A5-E61D-4B63-A929-0EDC89CE3B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20186" windowHeight="12800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>DimID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -288,6 +288,26 @@
   </si>
   <si>
     <t>FeatureCov[yijt=1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(Y0[All])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(LogDegSum[All]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(Dist[All]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(FeatureCov[All]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cov(Dist[All],FeatureCov[All])</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -326,7 +346,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,6 +362,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -382,6 +408,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -666,7 +694,7 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.52734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.234375" style="2" customWidth="1"/>
     <col min="3" max="16384" width="8.9375" style="2"/>
   </cols>
   <sheetData>
@@ -839,34 +867,34 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="9" t="s">
         <v>74</v>
       </c>
     </row>
@@ -874,6 +902,9 @@
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="B26" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
@@ -894,6 +925,9 @@
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="B30" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
@@ -904,11 +938,17 @@
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="B32" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="B33" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
@@ -918,6 +958,9 @@
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
         <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">

--- a/moment_list.xlsx
+++ b/moment_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\NetworkNNE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6D84A5-E61D-4B63-A929-0EDC89CE3B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D85110A-B8F3-4067-95A0-AC6191B630B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20186" windowHeight="12800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>DimID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -263,22 +263,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Y0[All]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dist[All]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LogDegSum[All]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeatureCov[All]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Dist[yijt=1]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -291,23 +275,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Var(Y0[All])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(LogDegSum[All]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(Dist[All]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(FeatureCov[All]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cov(Dist[All],FeatureCov[All])</t>
+    <t>Var(FeatureCov[yijt=0]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(LogDegSum[yijt=0]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cov(Dist[yijt=0],FeatureCov[yijt=0])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(Dist[yijt=0]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(Y0[yijt=0])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y0[yijt=0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dist[yijt=0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LogDegSum[yijt=0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FeatureCov[yijt=0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cov(Dist[yijt=1],FeatureCov[yijt=1])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var(Dist[yijt=1]）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -871,7 +879,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -879,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
@@ -887,7 +895,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -895,7 +903,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
@@ -926,7 +934,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
@@ -939,7 +947,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
@@ -947,7 +955,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
@@ -960,39 +968,39 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>75</v>
+      <c r="B37" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>76</v>
+      <c r="B38" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>77</v>
+      <c r="B39" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
@@ -1019,6 +1027,9 @@
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="B44" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
@@ -1028,6 +1039,9 @@
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">

--- a/moment_list.xlsx
+++ b/moment_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\NetworkNNE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D85110A-B8F3-4067-95A0-AC6191B630B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9151D8-58E2-43AA-A114-7277BF7881C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20186" windowHeight="12800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>DimID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -271,51 +271,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FeatureCov[yijt=1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(FeatureCov[yijt=0]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(LogDegSum[yijt=0]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cov(Dist[yijt=0],FeatureCov[yijt=0])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(Dist[yijt=0]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Var(Y0[yijt=0])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y0[yijt=0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dist[yijt=0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LogDegSum[yijt=0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FeatureCov[yijt=0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Cov(Dist[yijt=1],FeatureCov[yijt=1])</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Var(Dist[yijt=1]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cos(X)[yijt=1]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -879,7 +843,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -887,7 +851,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
@@ -895,7 +859,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -903,16 +867,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
@@ -934,7 +895,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
@@ -947,16 +908,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
@@ -967,41 +925,30 @@
       <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>70</v>
-      </c>
+      <c r="B36" s="9"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>71</v>
-      </c>
+      <c r="B37" s="9"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>72</v>
-      </c>
+      <c r="B38" s="9"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>73</v>
-      </c>
+      <c r="B39" s="9"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
@@ -1027,9 +974,6 @@
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
@@ -1039,9 +983,6 @@
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
